--- a/data/trans_bre/P1801_2016_2023-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1801_2016_2023-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>8,92</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 16,51</t>
+          <t>2,3; 16,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,67</t>
+          <t>2,38; 14,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 36,57</t>
+          <t>4,38; 35,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 27,35</t>
+          <t>4,09; 29,95</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,55%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 15,79</t>
+          <t>0,67; 15,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 6,09</t>
+          <t>-5,1; 7,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 34,87</t>
+          <t>1,08; 34,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 11,44</t>
+          <t>-8,67; 13,91</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-12,79</t>
+          <t>5,95</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-18,18%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 19,17</t>
+          <t>1,38; 19,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-34,1; 6,81</t>
+          <t>-2,32; 13,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 37,8</t>
+          <t>2,86; 38,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-40,93; 12,34</t>
+          <t>-4,18; 28,42</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,95</t>
+          <t>9,72</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 11,47</t>
+          <t>2,15; 11,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 33,49</t>
+          <t>5,24; 14,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 25,09</t>
+          <t>4,29; 25,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 68,22</t>
+          <t>10,16; 29,84</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,85</t>
+          <t>13,5</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 15,03</t>
+          <t>4,47; 15,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 12,26</t>
+          <t>7,98; 18,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 35,47</t>
+          <t>9,49; 35,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 26,92</t>
+          <t>17,01; 47,1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26,53</t>
+          <t>27,76</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122,54%</t>
+          <t>141,48%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,95; 40,63</t>
+          <t>28,67; 40,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16,58; 35,32</t>
+          <t>17,93; 35,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100,71; 215,41</t>
+          <t>99,37; 213,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53,42; 251,29</t>
+          <t>60,91; 261,44</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>7,75</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 12,99</t>
+          <t>8,08; 13,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 11,07</t>
+          <t>5,35; 10,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,13; 28,64</t>
+          <t>16,94; 29,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 21,82</t>
+          <t>10,83; 21,57</t>
         </is>
       </c>
     </row>
